--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N147_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N147_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.4528296195011</v>
+        <v>11.12358481316893</v>
       </c>
       <c r="D2" t="n">
-        <v>67.98544282706509</v>
+        <v>11.04763445939808</v>
       </c>
       <c r="E2" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F2" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.14692541386827</v>
+        <v>11.39887537975359</v>
       </c>
       <c r="D3" t="n">
-        <v>69.7339808945339</v>
+        <v>11.33177189536176</v>
       </c>
       <c r="E3" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F3" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.613474921773206</v>
+        <v>0.7496896747881461</v>
       </c>
       <c r="D4" t="n">
-        <v>4.659735635494757</v>
+        <v>0.757207040767898</v>
       </c>
       <c r="E4" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F4" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.71024157816026</v>
+        <v>8.240414256451043</v>
       </c>
       <c r="D5" t="n">
-        <v>50.72367034688744</v>
+        <v>8.242596431369209</v>
       </c>
       <c r="E5" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F5" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.51602664696085</v>
+        <v>6.096354330131137</v>
       </c>
       <c r="D6" t="n">
-        <v>37.32468883507147</v>
+        <v>6.065261935699114</v>
       </c>
       <c r="E6" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F6" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.42225977886849</v>
+        <v>5.431117214066131</v>
       </c>
       <c r="D7" t="n">
-        <v>33.12733766142074</v>
+        <v>5.38319236998087</v>
       </c>
       <c r="E7" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F7" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.890894360619247</v>
+        <v>0.7947703336006277</v>
       </c>
       <c r="D8" t="n">
-        <v>4.4504738300349</v>
+        <v>0.7232019973806713</v>
       </c>
       <c r="E8" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F8" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.88022687593092</v>
+        <v>9.893036867338775</v>
       </c>
       <c r="D9" t="n">
-        <v>61.37592602776072</v>
+        <v>9.973587979511118</v>
       </c>
       <c r="E9" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F9" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>75.48746873725618</v>
+        <v>12.26671366980413</v>
       </c>
       <c r="D10" t="n">
-        <v>75.98058287549311</v>
+        <v>12.34684471726763</v>
       </c>
       <c r="E10" t="n">
-        <v>25.44362726133456</v>
+        <v>4.134589429966867</v>
       </c>
       <c r="F10" t="n">
-        <v>25.54361244412318</v>
+        <v>4.150837022170017</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
